--- a/Backup/Presenças Individuais PAM Report.xlsx
+++ b/Backup/Presenças Individuais PAM Report.xlsx
@@ -61,14 +61,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
     <col min="2" max="2" width="14.0" customWidth="true"/>
     <col min="3" max="3" width="8.0" customWidth="true"/>
-    <col min="4" max="4" width="13.0" customWidth="true"/>
+    <col min="4" max="4" width="16.0" customWidth="true"/>
     <col min="5" max="5" width="16.0" customWidth="true"/>
+    <col min="6" max="6" width="8.0" customWidth="true"/>
+    <col min="7" max="7" width="8.0" customWidth="true"/>
+    <col min="8" max="8" width="8.0" customWidth="true"/>
+    <col min="9" max="9" width="13.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -89,12 +93,32 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>ID Da Empreendedoras</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Nome Empreendedora</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Cidade</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ciclo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Pesquisadores</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Nome Empreendedora</t>
         </is>
       </c>
     </row>
@@ -114,12 +138,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>PAM_2026_02</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ANCHA FRANCISCO LIMA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ANCHA FRANCISCO LIMA</t>
         </is>
       </c>
     </row>
@@ -139,12 +183,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>PAM_2026_03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ANDREA DE FATIMA COUTO MARIO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ANDREA DE FATIMA COUTO MARIO</t>
         </is>
       </c>
     </row>
@@ -164,12 +228,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>PAM_2026_07</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BEMVINDA HALIA MARIO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> BEMVINDA HALIA MARIO</t>
         </is>
       </c>
     </row>
@@ -189,12 +273,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>PAM_2026_10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CESALTINA DA GLORIA MATIAS JOAQUIM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CESALTINA DA GLORIA MATIAS JOAQUIM</t>
         </is>
       </c>
     </row>
@@ -214,12 +318,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>PAM_2026_52</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ESTEFANIA SAMUEL BOLACHA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ESTEFANIA SAMUEL BOLACHA</t>
         </is>
       </c>
     </row>
@@ -239,12 +363,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>PAM_2026_15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FATIMA SALVADOR AMADE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> FATIMA SALVADOR AMADE</t>
         </is>
       </c>
     </row>
@@ -264,12 +408,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>PAM_2026_49</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> INES BERNARDO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> INES BERNARDO</t>
         </is>
       </c>
     </row>
@@ -289,12 +453,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PAM_2026_20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ISAURA EVA ABILIO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ISAURA EVA ABILIO</t>
         </is>
       </c>
     </row>
@@ -314,12 +498,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>PAM_2026_27</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MADALENA CARIM MERAGE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> MADALENA CARIM MERAGE</t>
         </is>
       </c>
     </row>
@@ -339,12 +543,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>PAM_2026_29</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MARIAMO HANIFA ABACAR CHALE SALIMO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> MARIAMO HANIFA ABACAR CHALE SALIMO</t>
         </is>
       </c>
     </row>
@@ -364,12 +588,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>PAM_2026_31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MIMI IBRAIMO OMAR</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> MIMI IBRAIMO OMAR</t>
         </is>
       </c>
     </row>
@@ -389,12 +633,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>PAM_2026_35</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OLINDA CARLINDO NAMIRECA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OLINDA CARLINDO NAMIRECA</t>
         </is>
       </c>
     </row>
@@ -414,12 +678,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>PAM_2026_36</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OTILIA LUIS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OTILIA LUIS</t>
         </is>
       </c>
     </row>
@@ -439,12 +723,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>PAM_2026_37</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> REGINA MANUEL PASSURI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> REGINA MANUEL PASSURI</t>
         </is>
       </c>
     </row>
@@ -464,12 +768,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PAM_2026_38</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ROSA ERNESTO CASIMUCA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ROSA ERNESTO CASIMUCA</t>
         </is>
       </c>
     </row>
@@ -489,12 +813,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>PAM_2026_40</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SHEILA MACARIO ANTONIO  CUMANRARE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> SHEILA MACARIO ANTONIO  CUMANRARE</t>
         </is>
       </c>
     </row>
@@ -514,12 +858,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>PAM_2026_44</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TUCHA OSVALDO FERNANDO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> TUCHA OSVALDO FERNANDO</t>
         </is>
       </c>
     </row>
@@ -539,12 +903,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>PAM_2026_45</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> VIRGINIA ORLANDO AVELINO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> VIRGINIA ORLANDO AVELINO</t>
         </is>
       </c>
     </row>
@@ -564,12 +948,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>PAM_2026_46</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ZIBIA JOAO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ZIBIA JOAO</t>
         </is>
       </c>
     </row>
@@ -589,12 +993,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>PAM_2026_47</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ZINEIDE USSENE MARIO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ZINEIDE USSENE MARIO</t>
         </is>
       </c>
     </row>
@@ -614,12 +1038,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>PAM_2026_01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AMELIA AFUSSA ANTONIO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> AMELIA AFUSSA ANTONIO</t>
         </is>
       </c>
     </row>
@@ -639,12 +1083,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>PAM_2026_02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ANCHA FRANCISCO LIMA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ANCHA FRANCISCO LIMA</t>
         </is>
       </c>
     </row>
@@ -664,12 +1128,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>PAM_2026_03</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ANDREA DE FATIMA COUTO MARIO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ANDREA DE FATIMA COUTO MARIO</t>
         </is>
       </c>
     </row>
@@ -689,12 +1173,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>PAM_2026_01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AMELIA AFUSSA ANTONIO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> AMELIA AFUSSA ANTONIO</t>
         </is>
       </c>
     </row>
@@ -714,12 +1218,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>PAM_2026_07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BEMVINDA HALIA MARIO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> BEMVINDA HALIA MARIO</t>
         </is>
       </c>
     </row>
@@ -739,12 +1263,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>PAM_2026_10</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CESALTINA DA GLORIA MATIAS JOAQUIM</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CESALTINA DA GLORIA MATIAS JOAQUIM</t>
         </is>
       </c>
     </row>
@@ -764,12 +1308,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>PAM_2026_52</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ESTEFANIA SAMUEL BOLACHA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ESTEFANIA SAMUEL BOLACHA</t>
         </is>
       </c>
     </row>
@@ -789,12 +1353,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>PAM_2026_15</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FATIMA SALVADOR AMADE</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> FATIMA SALVADOR AMADE</t>
         </is>
       </c>
     </row>
@@ -814,12 +1398,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>PAM_2026_49</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> INES BERNARDO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> INES BERNARDO</t>
         </is>
       </c>
     </row>
@@ -839,12 +1443,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>PAM_2026_49</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> INES BERNARDO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> INES BERNARDO</t>
         </is>
       </c>
     </row>
@@ -864,12 +1488,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>PAM_2026_20</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ISAURA EVA ABILIO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ISAURA EVA ABILIO</t>
         </is>
       </c>
     </row>
@@ -889,12 +1533,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>PAM_2026_27</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MADALENA CARIM MERAGE</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> MADALENA CARIM MERAGE</t>
         </is>
       </c>
     </row>
@@ -914,12 +1578,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>PAM_2026_29</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MARIAMO HANIFA ABACAR CHALE SALIMO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> MARIAMO HANIFA ABACAR CHALE SALIMO</t>
         </is>
       </c>
     </row>
@@ -939,12 +1623,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>PAM_2026_31</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MIMI IBRAIMO OMAR</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> MIMI IBRAIMO OMAR</t>
         </is>
       </c>
     </row>
@@ -964,12 +1668,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>PAM_2026_35</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OLINDA CARLINDO NAMIRECA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OLINDA CARLINDO NAMIRECA</t>
         </is>
       </c>
     </row>
@@ -989,12 +1713,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>PAM_2026_36</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OTILIA LUIS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OTILIA LUIS</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1758,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>PAM_2026_37</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> REGINA MANUEL PASSURI</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> REGINA MANUEL PASSURI</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1803,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>PAM_2026_38</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ROSA ERNESTO CASIMUCA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ROSA ERNESTO CASIMUCA</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1848,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>PAM_2026_38</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ROSA ERNESTO CASIMUCA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ROSA ERNESTO CASIMUCA</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1893,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>PAM_2026_40</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SHEILA MACARIO ANTONIO  CUMANRARE</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> SHEILA MACARIO ANTONIO  CUMANRARE</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1938,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>PAM_2026_44</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TUCHA OSVALDO FERNANDO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> TUCHA OSVALDO FERNANDO</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1983,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>PAM_2026_45</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> VIRGINIA ORLANDO AVELINO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> VIRGINIA ORLANDO AVELINO</t>
         </is>
       </c>
     </row>
@@ -1164,12 +2028,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>PAM_2026_46</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ZIBIA JOAO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ZIBIA JOAO</t>
         </is>
       </c>
     </row>
@@ -1189,18 +2073,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>PAM_2026_47</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ZINEIDE USSENE MARIO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>Azarias</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ZINEIDE USSENE MARIO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46175.0</v>
+        <v>46272.0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1214,18 +2118,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_C4_05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+          <t xml:space="preserve"> ARCA BERNARDO BACIANO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Azarias</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46178.0</v>
+        <v>46273.0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1234,23 +2158,43 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Presente</t>
+          <t>Ausente</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_C4_07</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LATIZA AIUBA</t>
+          <t xml:space="preserve"> ATIJA ASSANE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Azarias</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46178.0</v>
+        <v>46273.0</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1264,18 +2208,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_C4_10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+          <t xml:space="preserve"> DANIELA AMISSE</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Azarias</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46178.0</v>
+        <v>46273.0</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1284,23 +2248,43 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Presente</t>
+          <t>Ausente</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_C4_12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t xml:space="preserve"> DINISIA DE JAMAL ALBERTO CARLOS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Azarias</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46176.0</v>
+        <v>46273.0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1314,18 +2298,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_C4_21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t xml:space="preserve"> FELIZARDA FELISBERTO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Azarias</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46177.0</v>
+        <v>46175.0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1339,18 +2343,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_48</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DULQUIFAL ASSANE SIMBA</t>
+          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46177.0</v>
+        <v>46178.0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1364,12 +2388,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+          <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -1389,18 +2433,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46181.0</v>
+        <v>46178.0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1414,18 +2478,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46181.0</v>
+        <v>46176.0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1439,18 +2523,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46181.0</v>
+        <v>46177.0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1464,18 +2568,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t xml:space="preserve"> DULQUIFAL ASSANE SIMBA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46182.0</v>
+        <v>46177.0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1489,18 +2613,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46182.0</v>
+        <v>46178.0</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1514,18 +2658,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GLORIA DA CONSTANCIA LOJA</t>
+          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46182.0</v>
+        <v>46181.0</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1539,18 +2703,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46182.0</v>
+        <v>46181.0</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1564,18 +2748,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46183.0</v>
+        <v>46181.0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1589,18 +2793,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARAVILHA JANUARIO  CARIA</t>
+          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46183.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1614,18 +2838,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46188.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1639,22 +2883,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+          <t xml:space="preserve"> GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46184.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1664,18 +2928,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_22</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46190.0</v>
+        <v>46182.0</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1684,27 +2968,47 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Presente</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_43</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SUZANA JOAQUIM VAQUINA</t>
+          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46189.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1714,22 +3018,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_C4_57</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t xml:space="preserve"> MARAVILHA JANUARIO  CARIA</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46190.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1739,22 +3063,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46190.0</v>
+        <v>46188.0</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1764,18 +3108,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_05</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46190.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1789,37 +3153,77 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_08</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46188.0</v>
+        <v>46190.0</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Presente</t>
+          <t>Ausente</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_42</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LATIZA AIUBA</t>
+          <t xml:space="preserve"> SUZANA JOAQUIM VAQUINA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -1839,12 +3243,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -1854,7 +3278,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1864,12 +3288,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_08</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -1889,22 +3333,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_24</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARAVILHA JANUARIO  CARIA</t>
+          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46209.0</v>
+        <v>46190.0</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1914,22 +3378,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_43</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46209.0</v>
+        <v>46188.0</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1939,22 +3423,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46209.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1964,18 +3468,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_16</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LATIZA AIUBA</t>
+          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46206.0</v>
+        <v>46190.0</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1989,22 +3513,42 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46211.0</v>
+        <v>46190.0</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2014,18 +3558,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_C4_57</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t xml:space="preserve"> MARAVILHA JANUARIO  CARIA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Activa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Ciclo 4</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46211.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2039,18 +3603,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_26</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46210.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2064,22 +3648,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_18</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46210.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2089,18 +3693,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+          <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46210.0</v>
+        <v>46206.0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2114,22 +3738,42 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_05</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46210.0</v>
+        <v>46211.0</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2139,18 +3783,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46210.0</v>
+        <v>46211.0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2164,22 +3828,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46218.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sessão Individual 5</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2189,22 +3873,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_43</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46218.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2214,22 +3918,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_22</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
           <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46218.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2239,18 +3963,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_13</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46191.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2264,18 +4008,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_13</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46203.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2289,22 +4053,42 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_24</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46211.0</v>
+        <v>46218.0</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 5</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2314,22 +4098,42 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46219.0</v>
+        <v>46218.0</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2339,18 +4143,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_22</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LATIZA AIUBA</t>
+          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46202.0</v>
+        <v>46218.0</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2364,22 +4188,42 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_17</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46210.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2389,22 +4233,42 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46219.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sessão Individual 5</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2414,22 +4278,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46218.0</v>
+        <v>46211.0</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2439,47 +4323,87 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46196.0</v>
+        <v>46219.0</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Presente</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46219.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2489,22 +4413,42 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_16</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LATIZA AIUBA</t>
+          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46185.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2514,22 +4458,42 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_16</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46197.0</v>
+        <v>46219.0</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 5</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2539,22 +4503,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_16</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46210.0</v>
+        <v>46218.0</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2564,47 +4548,87 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46219.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sessão Individual 5</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Presente</t>
+          <t>Ausente</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_18</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46218.0</v>
+        <v>46219.0</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sessão Individual 5</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2614,22 +4638,42 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+          <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46217.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2639,22 +4683,42 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_48</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46183.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sessão Individual 2</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2664,22 +4728,42 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_48</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46191.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sessão Individual 3</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2689,22 +4773,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_48</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46203.0</v>
+        <v>46219.0</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 5</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2714,18 +4818,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_48</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46210.0</v>
+        <v>46218.0</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2739,18 +4863,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46216.0</v>
+        <v>46217.0</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2764,22 +4908,42 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46217.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2789,18 +4953,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46216.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -2814,22 +4998,42 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46231.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2839,18 +5043,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
           <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46231.0</v>
+        <v>46210.0</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -2864,18 +5088,38 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46224.0</v>
+        <v>46216.0</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -2889,22 +5133,42 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_18</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46232.0</v>
+        <v>46217.0</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sessão Individual 5</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2914,22 +5178,42 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_43</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46231.0</v>
+        <v>46216.0</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2939,12 +5223,32 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_05</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -2954,7 +5258,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sessão Individual 5</t>
+          <t>Sessão Individual 6</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2964,12 +5268,32 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -2989,22 +5313,42 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_06</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46231.0</v>
+        <v>46224.0</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sessão Individual 5</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3014,18 +5358,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_05</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46231.0</v>
+        <v>46232.0</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3039,12 +5403,32 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_05</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -3054,7 +5438,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 6</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3064,18 +5448,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_16</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46232.0</v>
+        <v>46231.0</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3089,22 +5493,42 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_24</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LATIZA AIUBA</t>
+          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46232.0</v>
+        <v>46231.0</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 5</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3114,18 +5538,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_18</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46232.0</v>
+        <v>46231.0</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -3139,22 +5583,42 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_48</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46232.0</v>
+        <v>46231.0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sessão Individual 4</t>
+          <t>Sessão Individual 5</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3164,18 +5628,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_43</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46232.0</v>
+        <v>46231.0</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -3189,12 +5673,32 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_22</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -3204,7 +5708,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 5</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3214,18 +5718,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46238.0</v>
+        <v>46232.0</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3239,18 +5763,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_09</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46238.0</v>
+        <v>46232.0</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -3264,22 +5808,42 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_26</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46239.0</v>
+        <v>46232.0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3289,22 +5853,42 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_17</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46239.0</v>
+        <v>46232.0</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 4</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3314,18 +5898,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_13</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LATIZA AIUBA</t>
+          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46239.0</v>
+        <v>46232.0</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -3339,22 +5943,42 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_08</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46240.0</v>
+        <v>46238.0</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Sessão Individual 7</t>
+          <t>Sessão Individual 6</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3364,18 +5988,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_05</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46237.0</v>
+        <v>46238.0</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -3389,18 +6033,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_17</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46240.0</v>
+        <v>46239.0</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -3414,22 +6078,42 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_43</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46247.0</v>
+        <v>46239.0</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sessão Individual 7</t>
+          <t>Sessão Individual 6</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3439,22 +6123,42 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
           <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46240.0</v>
+        <v>46239.0</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sessão Individual 7</t>
+          <t>Sessão Individual 6</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3464,12 +6168,32 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_06</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -3489,22 +6213,42 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46245.0</v>
+        <v>46237.0</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sessão Individual 8</t>
+          <t>Sessão Individual 5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3514,18 +6258,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46241.0</v>
+        <v>46240.0</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -3539,12 +6303,32 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_13</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t xml:space="preserve"> ESMERALDA JORGE MURIRIUA</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -3564,22 +6348,42 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46241.0</v>
+        <v>46240.0</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 7</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3589,18 +6393,38 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_48</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46248.0</v>
+        <v>46240.0</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -3614,18 +6438,38 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_16</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46254.0</v>
+        <v>46245.0</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -3639,12 +6483,32 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_16</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+          <t xml:space="preserve"> FILOMENA AMINA DOMINGOS ALVEZ</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -3654,7 +6518,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sessão Individual 7</t>
+          <t>Sessão Individual 6</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3664,22 +6528,42 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_26</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sessão Individual 8</t>
+          <t>Sessão Individual 7</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3689,22 +6573,42 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_26</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46254.0</v>
+        <v>46241.0</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Sessão Individual 7</t>
+          <t>Sessão Individual 6</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3714,22 +6618,42 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_18</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
           <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46254.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sessão Individual 8</t>
+          <t>Sessão Individual 7</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3739,12 +6663,32 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_43</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LATIZA AIUBA</t>
+          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -3764,22 +6708,42 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_43</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+          <t xml:space="preserve"> TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46253.0</v>
+        <v>46241.0</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sessão Individual 8</t>
+          <t>Sessão Individual 7</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3789,18 +6753,38 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_08</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46255.0</v>
+        <v>46254.0</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -3814,22 +6798,42 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_08</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t xml:space="preserve"> BENUA FERNANDO VALENTIM INACIO BENE</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46247.0</v>
+        <v>46254.0</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sessão Individual 8</t>
+          <t>Sessão Individual 7</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3839,22 +6843,42 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_18</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46255.0</v>
+        <v>46254.0</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sessão Individual 9</t>
+          <t>Sessão Individual 8</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3864,18 +6888,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_25</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+          <t xml:space="preserve"> LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -3889,22 +6933,42 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_48</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t xml:space="preserve"> GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46247.0</v>
+        <v>46253.0</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Sessão Individual 7</t>
+          <t>Sessão Individual 8</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3914,18 +6978,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_09</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+          <t xml:space="preserve"> CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46254.0</v>
+        <v>46255.0</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -3939,22 +7023,42 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_26</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+          <t xml:space="preserve"> LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46244.0</v>
+        <v>46247.0</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 8</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3964,22 +7068,42 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46253.0</v>
+        <v>46255.0</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sessão Individual 7</t>
+          <t>Sessão Individual 9</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3989,12 +7113,32 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_50</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+          <t xml:space="preserve"> ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -4014,18 +7158,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_18</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+          <t xml:space="preserve"> GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46245.0</v>
+        <v>46247.0</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -4039,18 +7203,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_05</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46255.0</v>
+        <v>46254.0</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -4064,18 +7248,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_05</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+          <t xml:space="preserve"> ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46240.0</v>
+        <v>46244.0</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4089,18 +7293,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_17</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46248.0</v>
+        <v>46253.0</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4114,18 +7338,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_17</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46254.0</v>
+        <v>46261.0</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4139,22 +7383,42 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_17</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+          <t xml:space="preserve"> FRANCISCA LUCIANO BOMES</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46240.0</v>
+        <v>46245.0</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Sessão Individual 5</t>
+          <t>Sessão Individual 7</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4164,22 +7428,42 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_06</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46248.0</v>
+        <v>46255.0</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sessão Individual 6</t>
+          <t>Sessão Individual 8</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4189,22 +7473,42 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_06</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+          <t xml:space="preserve"> ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Sessão Individual 7</t>
+          <t>Sessão Individual 6</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4214,37 +7518,302 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>PAM_2026_24</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
+        <v>46248.0</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sessão Individual 7</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Presente</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>PAM_2026_24</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46254.0</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Sessão Individual 8</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Presente</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PAM_2026_24</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> KADHJA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46240.0</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Sessão Individual 5</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Presente</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PAM_2026_22</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46248.0</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sessão Individual 6</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Presente</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PAM_2026_22</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46254.0</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Sessão Individual 7</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Presente</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>PAM_2026_22</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
         <v>46261.0</v>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Sessão Individual 8</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Presente</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Luisa</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Presente</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>PAM_2026_22</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
         <is>
           <t xml:space="preserve"> JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Desistente</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
     </row>
@@ -4509,13 +8078,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B5067E6-9ED0-40A1-ACD5-E130498D0E03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25E3A10E-821F-45C7-AF41-735EF9B365A1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8A35855-431F-4487-A061-577F052A99A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F802DFE-F648-4042-B63D-93A0369DDF8B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FBE3AC5-3D2D-4FEC-92CC-99ED4FA9F9AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D1556B-739F-4468-90F6-B2F3431D704F}"/>
 </file>